--- a/site/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,6 +592,72 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Directory</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KRZXNH6R5GZ0AEMNSNNTX6BK</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KRZXNH6R5GZ0AEMNSNNTX6BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Entra ID Application Settings</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KRZZRVGSTRJM6999JFAP478J</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KRZZRVGSTRJM6999JFAP478J</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Writeback Settings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KS029C113DVGXE21QK1SK0E9</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS029C113DVGXE21QK1SK0E9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,12 +649,56 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KS029C113DVGXE21QK1SK0E9</t>
+          <t>h_01KS06157W1F8XZJ82X34B3PQH</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS029C113DVGXE21QK1SK0E9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS06157W1F8XZJ82X34B3PQH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KS06157WYJGAJCAK99BH8GJG</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS06157WYJGAJCAK99BH8GJG</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ADP Application Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KS06157W2NNBJH667KQXM109</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS06157W2NNBJH667KQXM109</t>
         </is>
       </c>
     </row>

--- a/site/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,130 +573,174 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Directory</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>h_01KRZXNH6R5GZ0AEMNSNNTX6BK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KRZXNH6R5GZ0AEMNSNNTX6BK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Directory</t>
+          <t>Directory Settings</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KRZXNH6R5GZ0AEMNSNNTX6BK</t>
+          <t>h_01KRZZRVGSTRJM6999JFAP478J</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KRZXNH6R5GZ0AEMNSNNTX6BK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KRZZRVGSTRJM6999JFAP478J</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Entra ID Application Settings</t>
+          <t>Data Synchronization Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KRZZRVGSTRJM6999JFAP478J</t>
+          <t>h_01KS7CWZ3SM6PFYW470KBJR45C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KRZZRVGSTRJM6999JFAP478J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS7CWZ3SM6PFYW470KBJR45C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Writeback Settings</t>
+          <t>Conditional Writeback Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KS06157W1F8XZJ82X34B3PQH</t>
+          <t>h_01KS7EYPT5R5R60900YZ4SDYP9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS06157W1F8XZJ82X34B3PQH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS7EYPT5R5R60900YZ4SDYP9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Application Setting</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KS06157WYJGAJCAK99BH8GJG</t>
+          <t>h_01KS7EYQNAVT985NR9FA2P8WSJ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS06157WYJGAJCAK99BH8GJG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS7EYQNAVT985NR9FA2P8WSJ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Writeback Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KS06157W1F8XZJ82X34B3PQH</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS06157W1F8XZJ82X34B3PQH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KS06157WYJGAJCAK99BH8GJG</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS06157WYJGAJCAK99BH8GJG</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>ADP Application Settings</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>h_01KS06157W2NNBJH667KQXM109</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS06157W2NNBJH667KQXM109</t>
         </is>

--- a/site/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,6 +746,72 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Execution Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KS7JYH0ZFSHD8E247N3M4J8Z</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS7JYH0ZFSHD8E247N3M4J8Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KS7K1N0D3FJKM470R3E359Q8</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS7K1N0D3FJKM470R3E359Q8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Operational Settings</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KS7K248GDK85V96XFQVT95PG</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ADP-Workforce-Now-Writeback-Integration-Guide/#h_01KS7K248GDK85V96XFQVT95PG</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
